--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487690_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487690_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9431</v>
+        <v>5.8462</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7582</v>
+        <v>5.8793</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1849</v>
+        <v>-0.0331</v>
       </c>
       <c r="G2" t="n">
         <v>5.1071</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0599</v>
+        <v>-0.037</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1346</v>
+        <v>0.2557</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0747</v>
+        <v>-0.2927</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>L. SCHIEBELHUT LUIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9347</v>
+        <v>4.9834</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9634</v>
+        <v>5.386</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0287</v>
+        <v>-0.4025</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0731</v>
+        <v>4.5126</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6896</v>
+        <v>3.045</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3835</v>
+        <v>1.4676</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3248</v>
+        <v>4.7588</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6632</v>
+        <v>3.4191</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6616</v>
+        <v>1.3397</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2517</v>
+        <v>-0.2462</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0263</v>
+        <v>-0.374</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2781</v>
+        <v>0.1279</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8914</v>
+        <v>0.0544</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6386</v>
+        <v>0.0914</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7472</v>
+        <v>-0.037</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. SCHIEBELHUT LUIS</t>
+          <t>D. GARCIA DELGADO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5046</v>
+        <v>4.0375</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1252</v>
+        <v>3.4601</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6206</v>
+        <v>0.5774</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5126</v>
+        <v>3.6367</v>
       </c>
       <c r="H4" t="n">
-        <v>3.045</v>
+        <v>1.0274</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4676</v>
+        <v>2.6093</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7588</v>
+        <v>3.5319</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4191</v>
+        <v>1.0504</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3397</v>
+        <v>2.4814</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2462</v>
+        <v>0.1048</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.374</v>
+        <v>-0.0231</v>
       </c>
       <c r="O4" t="n">
         <v>0.1279</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4244</v>
+        <v>-0.6455</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1694</v>
+        <v>-0.0718</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.255</v>
+        <v>-0.5737</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9418</v>
+        <v>-0.894</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4477</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA DELGADO</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5009</v>
+        <v>3.967</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0597</v>
+        <v>4.023</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4412</v>
+        <v>-0.056</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6367</v>
+        <v>3.0731</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0274</v>
+        <v>0.6896</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6093</v>
+        <v>2.3835</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5319</v>
+        <v>3.3248</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0504</v>
+        <v>0.6632</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4814</v>
+        <v>2.6616</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1048</v>
+        <v>-0.2517</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0231</v>
+        <v>0.0263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1279</v>
+        <v>-0.2781</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1821</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4722</v>
+        <v>0.6982</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7099</v>
+        <v>-0.7744</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5586</v>
+        <v>3.0218</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2901</v>
+        <v>2.0614</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2684</v>
+        <v>0.9604</v>
       </c>
       <c r="G6" t="n">
-        <v>1.129</v>
+        <v>2.3333</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2411</v>
+        <v>2.2409</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1121</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3803</v>
+        <v>2.869</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6694</v>
+        <v>2.0926</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.289</v>
+        <v>0.7764</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2513</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5718</v>
+        <v>0.1483</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4296</v>
+        <v>-0.904</v>
       </c>
       <c r="T6" t="n">
-        <v>0.268</v>
+        <v>-0.0718</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1615</v>
+        <v>-0.8322000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6119</v>
+        <v>0.2343</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6119</v>
+        <v>0.2343</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>D. VAL GUTIERREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3367</v>
+        <v>2.5787</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5398</v>
+        <v>1.0705</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7969000000000001</v>
+        <v>1.5082</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3333</v>
+        <v>0.5458</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2409</v>
+        <v>2.2525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09229999999999999</v>
+        <v>-1.7067</v>
       </c>
       <c r="J7" t="n">
-        <v>2.869</v>
+        <v>0.8087</v>
       </c>
       <c r="K7" t="n">
         <v>2.0926</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7764</v>
+        <v>-1.284</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.2629</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1483</v>
+        <v>0.1598</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.4227</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3582</v>
+        <v>2.3284</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.589</v>
+        <v>-0.0611</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5933</v>
+        <v>0.2619</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9957</v>
+        <v>-0.323</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2343</v>
+        <v>-0.2343</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2523</v>
+        <v>2.1313</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0761</v>
+        <v>1.2716</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8238</v>
+        <v>0.8596</v>
       </c>
       <c r="G8" t="n">
-        <v>3.188</v>
+        <v>1.129</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2841</v>
+        <v>3.2411</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0961</v>
+        <v>-2.1121</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3844</v>
+        <v>1.3803</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5972</v>
+        <v>2.6694</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2129</v>
+        <v>-1.289</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1963</v>
+        <v>-0.2513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3131</v>
+        <v>0.5718</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1168</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3941</v>
+        <v>0.0023</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8142</v>
+        <v>0.2495</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4201</v>
+        <v>-0.2473</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9418</v>
+        <v>0.6119</v>
       </c>
       <c r="W8" t="n">
-        <v>1.788</v>
+        <v>0.6119</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. VAL GUTIERREZ</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9115</v>
+        <v>1.4698</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3488</v>
+        <v>2.3754</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5627</v>
+        <v>-0.9056</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5458</v>
+        <v>3.188</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2525</v>
+        <v>4.2841</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7067</v>
+        <v>-1.0961</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8087</v>
+        <v>3.3844</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0926</v>
+        <v>4.5972</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.284</v>
+        <v>-1.2129</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2629</v>
+        <v>-0.1963</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1598</v>
+        <v>-0.3131</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4227</v>
+        <v>0.1168</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3284</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>2.5224</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.3883</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4599</v>
+        <v>0.1135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2685</v>
+        <v>-0.5019</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2343</v>
+        <v>-0.9418</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2343</v>
+        <v>-2.7298</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0126</v>
+        <v>0.4028</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1191</v>
+        <v>0.2418</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1065</v>
+        <v>0.1611</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8022</v>
@@ -1234,13 +1234,13 @@
         <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5581</v>
+        <v>-0.1427</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2299</v>
+        <v>0.1309</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3282</v>
+        <v>-0.2736</v>
       </c>
       <c r="V10" t="n">
         <v>0.3776</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1498</v>
+        <v>0.0437</v>
       </c>
       <c r="E11" t="n">
-        <v>1.7742</v>
+        <v>1.6952</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.924</v>
+        <v>-1.6515</v>
       </c>
       <c r="G11" t="n">
         <v>3.2075</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9096</v>
+        <v>-0.7161</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3163</v>
+        <v>0.2372</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2259</v>
+        <v>-0.9533</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6197</v>
+        <v>-0.2232</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0418</v>
+        <v>-0.2942</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5778</v>
+        <v>0.0711</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0667</v>
+        <v>0.6472</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2636</v>
+        <v>2.1898</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3303</v>
+        <v>-1.5427</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3906</v>
+        <v>0.8144</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5026</v>
+        <v>1.4006</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8931</v>
+        <v>-0.5861</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4573</v>
+        <v>-0.1673</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7662</v>
+        <v>0.7893</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2235</v>
+        <v>-0.9565</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1390,28 +1390,28 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0112</v>
+        <v>-0.5883</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2557</v>
+        <v>-0.1385</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2445</v>
+        <v>-0.4497</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5642</v>
+        <v>-0.2821</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8462</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,40 +1423,40 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.6499</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6156</v>
+        <v>0.2005</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.147</v>
+        <v>-0.8504</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6472</v>
+        <v>-0.0667</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1898</v>
+        <v>0.2636</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5427</v>
+        <v>-0.3303</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8144</v>
+        <v>0.3906</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4006</v>
+        <v>-0.5026</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5861</v>
+        <v>0.8931</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1673</v>
+        <v>-0.4573</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7893</v>
+        <v>0.7662</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9565</v>
+        <v>-1.2235</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1468,22 +1468,22 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1276</v>
+        <v>-0.0191</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4599</v>
+        <v>0.498</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.517</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2821</v>
+        <v>-0.5642</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2821</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.3977</v>
+        <v>27.6091</v>
       </c>
       <c r="E14" t="n">
-        <v>26.159</v>
+        <v>27.3706</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2387000000000003</v>
+        <v>0.2386999999999997</v>
       </c>
       <c r="G14" t="n">
         <v>26.5114</v>
@@ -1516,7 +1516,7 @@
         <v>21.7007</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8106</v>
+        <v>4.810600000000002</v>
       </c>
       <c r="J14" t="n">
         <v>30.1419</v>
@@ -1537,7 +1537,7 @@
         <v>-5.5335</v>
       </c>
       <c r="P14" t="n">
-        <v>9.701599999999999</v>
+        <v>9.701600000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.672</v>
@@ -1546,19 +1546,19 @@
         <v>20.3735</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.7329</v>
+        <v>-3.5217</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0428</v>
+        <v>2.2542</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.776</v>
+        <v>-5.7758</v>
       </c>
       <c r="V14" t="n">
         <v>-5.082100000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>5.646199999999999</v>
+        <v>5.6462</v>
       </c>
       <c r="X14" t="n">
         <v>-10.7281</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9843</v>
+        <v>1.9748</v>
       </c>
       <c r="E15" t="n">
-        <v>3.704</v>
+        <v>3.5038</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7197</v>
+        <v>-1.5289</v>
       </c>
       <c r="G15" t="n">
         <v>0.148</v>
@@ -1624,13 +1624,13 @@
         <v>0.5821</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3706</v>
+        <v>0.3611</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5103</v>
+        <v>0.3101</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1397</v>
+        <v>0.051</v>
       </c>
       <c r="V15" t="n">
         <v>1.2716</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2841</v>
+        <v>1.7151</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1288</v>
+        <v>0.1715</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4129</v>
+        <v>1.5435</v>
       </c>
       <c r="G16" t="n">
         <v>0.8299</v>
@@ -1702,13 +1702,13 @@
         <v>0.3881</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.4971</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1694</v>
+        <v>0.1309</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2355</v>
+        <v>0.3662</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0246</v>
+        <v>-0.546</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9093</v>
+        <v>2.9083</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8847</v>
+        <v>-3.4543</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9318</v>
@@ -1780,13 +1780,13 @@
         <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6265</v>
+        <v>1.0559</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0401</v>
+        <v>1.0391</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4136</v>
+        <v>0.0168</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8407</v>
+        <v>-1.0014</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3258</v>
+        <v>0.9254</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1665</v>
+        <v>-1.9268</v>
       </c>
       <c r="G18" t="n">
         <v>-4.0853</v>
@@ -1858,13 +1858,13 @@
         <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4551</v>
+        <v>0.2944</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7413</v>
+        <v>0.3409</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2862</v>
+        <v>-0.0465</v>
       </c>
       <c r="V18" t="n">
         <v>3.9537</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8985</v>
+        <v>-1.804</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2602</v>
+        <v>1.3603</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1587</v>
+        <v>-3.1643</v>
       </c>
       <c r="G19" t="n">
         <v>-0.21</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7638</v>
+        <v>0.8583</v>
       </c>
       <c r="T19" t="n">
-        <v>0.268</v>
+        <v>0.3681</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4958</v>
+        <v>0.4901</v>
       </c>
       <c r="V19" t="n">
         <v>-1.6761</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0104</v>
+        <v>-2.9203</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2084</v>
+        <v>-2.3417</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.802</v>
+        <v>-0.5786</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6465</v>
+        <v>-1.52</v>
       </c>
       <c r="H20" t="n">
-        <v>0.36</v>
+        <v>-2.7674</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0065</v>
+        <v>1.2474</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4961</v>
+        <v>0.3069</v>
       </c>
       <c r="K20" t="n">
-        <v>1.001</v>
+        <v>-0.9516</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5049</v>
+        <v>1.2585</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1425</v>
+        <v>-1.827</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.641</v>
+        <v>-1.8158</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5015</v>
+        <v>-0.0111</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1763</v>
+        <v>0.54</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5955</v>
+        <v>0.4559</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4192</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3463</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4965</v>
+        <v>-2.9498</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5419</v>
+        <v>-0.3085</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9546</v>
+        <v>-2.6413</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.52</v>
+        <v>-1.6465</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7674</v>
+        <v>0.36</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2474</v>
+        <v>-2.0065</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3069</v>
+        <v>0.4961</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9516</v>
+        <v>1.001</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2585</v>
+        <v>-0.5049</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.827</v>
+        <v>-2.1425</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8158</v>
+        <v>-0.641</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0111</v>
+        <v>-1.5015</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9403</v>
+        <v>-0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0361</v>
+        <v>0.2369</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2557</v>
+        <v>0.4954</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2918</v>
+        <v>-0.2585</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.3463</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0164</v>
       </c>
     </row>
     <row r="22">
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7277</v>
+        <v>-3.027</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4928</v>
+        <v>0.2079</v>
       </c>
       <c r="F22" t="n">
         <v>-3.2349</v>
@@ -2170,10 +2170,10 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3275</v>
+        <v>0.3732</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2905</v>
+        <v>0.4102</v>
       </c>
       <c r="U22" t="n">
         <v>-0.037</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3154</v>
+        <v>-3.7392</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2521</v>
+        <v>-2.0519</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0633</v>
+        <v>-1.6873</v>
       </c>
       <c r="G23" t="n">
         <v>-5.9871</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7523</v>
+        <v>1.3285</v>
       </c>
       <c r="T23" t="n">
-        <v>0.96</v>
+        <v>1.1602</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2077</v>
+        <v>0.1683</v>
       </c>
       <c r="V23" t="n">
         <v>2.2776</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4621</v>
+        <v>-3.9555</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3264</v>
+        <v>-0.926</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1358</v>
+        <v>-3.0295</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9348</v>
@@ -2326,13 +2326,13 @@
         <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1393</v>
+        <v>0.3673</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0348</v>
+        <v>0.3656</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1045</v>
+        <v>0.0017</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.9395</v>
+        <v>-8.1425</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4876</v>
+        <v>-3.6878</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.4519</v>
+        <v>-4.4547</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6138</v>
@@ -2404,13 +2404,13 @@
         <v>0.9702</v>
       </c>
       <c r="S25" t="n">
-        <v>1.0251</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8995</v>
+        <v>0.6993</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1256</v>
+        <v>0.1228</v>
       </c>
       <c r="V25" t="n">
         <v>0.7239</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-26.3978</v>
+        <v>-24.3958</v>
       </c>
       <c r="E26" t="n">
         <v>-0.2386999999999997</v>
       </c>
       <c r="F26" t="n">
-        <v>-26.1592</v>
+        <v>-24.1571</v>
       </c>
       <c r="G26" t="n">
         <v>-26.5113</v>
@@ -2482,13 +2482,13 @@
         <v>10.6718</v>
       </c>
       <c r="S26" t="n">
-        <v>4.733</v>
+        <v>6.7348</v>
       </c>
       <c r="T26" t="n">
         <v>5.7757</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0428</v>
+        <v>0.959</v>
       </c>
       <c r="V26" t="n">
         <v>5.082000000000001</v>
